--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC118887-EAD4-46CC-A93A-F313ECBACAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB8236-8F8E-4FA8-B35E-42AA5890EA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -45,9 +45,6 @@
     <t>desc</t>
   </si>
   <si>
-    <t>price</t>
-  </si>
-  <si>
     <t>icon</t>
   </si>
   <si>
@@ -75,44 +72,98 @@
     <t>描述</t>
   </si>
   <si>
-    <t>价格</t>
-  </si>
-  <si>
     <t>图片路径</t>
   </si>
   <si>
-    <t>灵晶微体</t>
-  </si>
-  <si>
-    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换少量灵晶币。</t>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem2]</t>
-  </si>
-  <si>
-    <t>灵晶体</t>
-  </si>
-  <si>
-    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换中量灵晶币。</t>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem3]</t>
-  </si>
-  <si>
-    <t>灵晶完全体</t>
-  </si>
-  <si>
-    <t>菱形晶体内部闪耀着变幻莫测的色彩，可以兑换大量灵晶币。</t>
-  </si>
-  <si>
-    <t>Assets/UI/Items/Items.spriteatlas[SpriteItem4]</t>
+    <t>模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一枚金灿灿的模拟币，可以用来购物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_simulation_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一堆模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>几枚金灿灿的模拟币，可以用来购物</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_coin_stack]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具折扣券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>家具折扣券~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_furniture_coupon]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神秘礼盒~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_gift_box]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IT技能证书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IT技能证书~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_ability_certificate]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修技能证书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>维修技能证书~</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rewardScale</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励面板下的缩放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,6 +174,14 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -149,8 +208,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -428,14 +490,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="60.44140625" customWidth="1"/>
-    <col min="5" max="5" width="7.21875" customWidth="1"/>
-    <col min="6" max="6" width="43.5546875" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -454,119 +516,170 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
+      <c r="F2" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
+      <c r="F4" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>50</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
+      <c r="F5">
+        <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>500</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
+      <c r="F6">
+        <v>4000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>1002</v>
-      </c>
-      <c r="C7" t="s">
+        <v>2000</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>3000</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7">
-        <v>2000</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="D8" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>4000</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>4001</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
+        <v>3600</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBB8236-8F8E-4FA8-B35E-42AA5890EA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AEC606-8029-4F1A-9A6C-B14676B85C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4284" yWindow="2532" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -75,10 +75,6 @@
     <t>图片路径</t>
   </si>
   <si>
-    <t>模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一枚金灿灿的模拟币，可以用来购物</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -156,6 +152,21 @@
   </si>
   <si>
     <t>奖励面板下的缩放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精美的时间币，可以用来抽奖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Lottery/SpriteAtlas.spriteatlasv2[icon_lottery_coin]</t>
+  </si>
+  <si>
+    <t>一枚模拟币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -174,6 +185,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -490,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" customWidth="1"/>
@@ -517,7 +529,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -537,7 +549,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -557,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -577,7 +589,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -585,13 +597,13 @@
         <v>1000</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F5">
         <v>2500</v>
@@ -602,13 +614,13 @@
         <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F6">
         <v>4000</v>
@@ -616,69 +628,86 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>2000</v>
+        <v>1010</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="F7">
-        <v>3200</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>4200</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>3600</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10">
+        <v>4000</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11">
         <v>4001</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10">
+      <c r="E11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11">
         <v>3600</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65AEC606-8029-4F1A-9A6C-B14676B85C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E7FA53-F605-4541-8DB9-489D5BAE036B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4284" yWindow="2532" windowWidth="23040" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -167,6 +167,22 @@
   </si>
   <si>
     <t>一枚模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>canUse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1为可在背包使用</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -502,17 +518,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="64.125" customWidth="1"/>
+    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,8 +548,11 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -551,8 +571,11 @@
       <c r="F2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -571,8 +594,11 @@
       <c r="F3" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -591,8 +617,11 @@
       <c r="F4" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -609,7 +638,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -626,7 +655,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1010</v>
       </c>
@@ -643,7 +672,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2000</v>
       </c>
@@ -660,7 +689,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>3000</v>
       </c>
@@ -676,8 +705,11 @@
       <c r="F9">
         <v>4200</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>4000</v>
       </c>
@@ -694,7 +726,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>4001</v>
       </c>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E7FA53-F605-4541-8DB9-489D5BAE036B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB94606-9C50-43BD-905C-E264D8B6468F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>##var</t>
   </si>
@@ -171,14 +171,6 @@
   </si>
   <si>
     <t>canUse</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c,s</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -518,18 +510,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.125" customWidth="1"/>
     <col min="3" max="3" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="51.875" customWidth="1"/>
     <col min="5" max="5" width="64.125" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -546,13 +539,15 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -572,10 +567,12 @@
         <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -595,10 +592,12 @@
         <v>32</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>32</v>
+      </c>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -615,13 +614,15 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -634,11 +635,11 @@
       <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -651,11 +652,11 @@
       <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1010</v>
       </c>
@@ -668,11 +669,11 @@
       <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>4000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2000</v>
       </c>
@@ -685,11 +686,11 @@
       <c r="E8" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>3000</v>
       </c>
@@ -703,13 +704,13 @@
         <v>24</v>
       </c>
       <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
         <v>4200</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>4000</v>
       </c>
@@ -722,11 +723,11 @@
       <c r="E10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>4001</v>
       </c>
@@ -739,7 +740,7 @@
       <c r="E11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>3600</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB94606-9C50-43BD-905C-E264D8B6468F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB7EB96-9199-4D93-845F-E2586F23FEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -103,10 +103,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_furniture_coupon]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>神秘礼盒</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -115,10 +111,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_gift_box]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>IT技能证书</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -127,10 +119,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_ability_certificate]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>维修技能证书</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,6 +163,18 @@
   </si>
   <si>
     <t>1为可在背包使用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_furniture_coupon]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_gift_box]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_ability_certificate]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -511,18 +511,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="13.5" customWidth="1"/>
-    <col min="4" max="4" width="51.875" customWidth="1"/>
-    <col min="5" max="5" width="64.125" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="5" max="5" width="64.109375" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="9" width="26.875" customWidth="1"/>
+    <col min="7" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,15 +539,15 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -564,15 +564,15 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -589,15 +589,15 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -614,20 +614,20 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
@@ -639,7 +639,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -656,24 +656,24 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1010</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G7">
         <v>4000</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>2000</v>
       </c>
@@ -684,24 +684,24 @@
         <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G8">
         <v>3200</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>3000</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -710,35 +710,35 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>4000</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>3600</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>4001</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>3600</v>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB7EB96-9199-4D93-845F-E2586F23FEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA0AD53-1645-4856-89CC-3B5DB10BC828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -79,10 +79,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_simulation_coin]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>一堆模拟币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -91,10 +87,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlas.spriteatlasv2[icon_coin_stack]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>家具折扣券</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,6 +167,14 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_ability_certificate]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_simulation_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_stack]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,10 +539,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -564,10 +564,10 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
@@ -589,10 +589,10 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
@@ -614,10 +614,10 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -627,13 +627,13 @@
         <v>1000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="G5">
         <v>2500</v>
@@ -644,13 +644,13 @@
         <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>4000</v>
@@ -661,13 +661,13 @@
         <v>1010</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="G7">
         <v>4000</v>
@@ -678,13 +678,13 @@
         <v>2000</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G8">
         <v>3200</v>
@@ -695,13 +695,13 @@
         <v>3000</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -715,13 +715,13 @@
         <v>4000</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G10">
         <v>3600</v>
@@ -732,13 +732,13 @@
         <v>4001</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G11">
         <v>3600</v>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA0AD53-1645-4856-89CC-3B5DB10BC828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7179045A-AE9D-4F13-9E4D-B47F05386F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -75,18 +75,6 @@
     <t>图片路径</t>
   </si>
   <si>
-    <t>一枚金灿灿的模拟币，可以用来购物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一堆模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>几枚金灿灿的模拟币，可以用来购物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>家具折扣券</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,13 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>精美的时间币，可以用来抽奖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Lottery/SpriteAtlas.spriteatlasv2[icon_lottery_coin]</t>
-  </si>
-  <si>
     <t>一枚模拟币</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -170,11 +151,103 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_simulation_coin]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_stack]</t>
+    <t>凝结着一小段时光的特殊货币，投入时光礼物箱，或许能换回一份来自未来的惊喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼓鼓钱袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一叠模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一枚亮晶晶的模拟币，使用后获取少量模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一叠金灿灿的模拟币，使用后获取一些模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钱袋已经被撑得圆滚滚的，使用后获取中量模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一箱模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箱子里全是模拟币，使用后获取大量模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>璀璨金库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在，需要担心的是该怎么把钱花完</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用奖池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,1000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,5000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,10000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,100,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,500,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -228,11 +301,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,15 +589,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
+    <col min="4" max="4" width="74.5546875" customWidth="1"/>
     <col min="5" max="5" width="64.109375" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="8" width="21.44140625" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="2" customWidth="1"/>
     <col min="9" max="9" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -539,12 +619,14 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>48</v>
+      </c>
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -564,12 +646,14 @@
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -589,12 +673,14 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -614,12 +700,14 @@
         <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -627,16 +715,22 @@
         <v>1000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="G5">
         <v>2500</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -644,103 +738,178 @@
         <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="G6">
         <v>4000</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>1010</v>
+        <v>1002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
       </c>
       <c r="G7">
         <v>4000</v>
       </c>
+      <c r="H7" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B8">
-        <v>2000</v>
+        <v>1003</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>3200</v>
+        <v>4500</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9">
-        <v>3000</v>
+        <v>1004</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9">
-        <v>4200</v>
+        <v>4000</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10">
+        <v>1010</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
         <v>4000</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10">
-        <v>3600</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11">
+        <v>2000</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>3000</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>4000</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14">
         <v>4001</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11">
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14">
         <v>3600</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7179045A-AE9D-4F13-9E4D-B47F05386F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0225CF-38BB-4C55-87A1-E98D49777290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,8 +30,77 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>111</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{A560902B-8CB5-4789-8FFD-EAD2CC08AED6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>111:
+1000 为基础属性相关道具</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+2000 为一些功能性道具
+3000 为一些稀有道具
+4000 为零工所需道具</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{0B62592B-BBDE-4669-870C-25B14286F5E8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>111:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 普通
+2 稀有
+3 史诗
+4 传说
+5 神话</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="141">
   <si>
     <t>##var</t>
   </si>
@@ -91,22 +160,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IT技能证书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IT技能证书~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修技能证书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>维修技能证书~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rewardScale</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -147,10 +200,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_ability_certificate]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>凝结着一小段时光的特殊货币，投入时光礼物箱，或许能换回一份来自未来的惊喜</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -248,6 +297,333 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电动踏板车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厢式货车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拧下车把，城市的每条小路都能变成赚钱捷径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建筑许可证书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_3]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装得下半座仓库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>薄薄一张纸，却能打开大型工程的厚重大门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版式启蒙册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣传样机册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌识别手册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展陈设计证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵感数位板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hadeep教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MySOL教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlty教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wwb三剑客教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeiX教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教文字和图片各就各位，拯救摇摇欲坠的海报</t>
+  </si>
+  <si>
+    <t>接住稍纵即逝的灵感，再把它们画成可以交稿的样子</t>
+  </si>
+  <si>
+    <t>提前看看成品，避免创意只活在想象之中</t>
+  </si>
+  <si>
+    <t>让颜色、图形和字体一眼看出是同一家人</t>
+  </si>
+  <si>
+    <t>获得让平面创意站起来，并占满整个展厅的资格</t>
+  </si>
+  <si>
+    <t>集齐结构、样式与交互，网页终于不再各长各的</t>
+  </si>
+  <si>
+    <t>小小页面装下大大功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教一群机器分头搬数据</t>
+  </si>
+  <si>
+    <t>从拖动一个方块开始，不知不觉搭出一整个世界</t>
+  </si>
+  <si>
+    <t>让四处乱跑的数据排好队</t>
+  </si>
+  <si>
+    <t>灵感钢笔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖点卡册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采访录音笔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧本打字机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>策划档案箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础维修工具包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管路维护套装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能万用表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型检修箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精密校准箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东西不算多，但足够让坏掉的家电重新反省</t>
+  </si>
+  <si>
+    <t>专治滴答作响，以及半夜突然有想法的水管</t>
+  </si>
+  <si>
+    <t>电路虽然不会说话，但屏幕上的波形很会告密</t>
+  </si>
+  <si>
+    <t>拧紧螺丝已经不够，让整台设备重新升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专门处理肉眼看不见、维修报价却看得很清楚的问题</t>
+  </si>
+  <si>
+    <t>负责把路过脑海的句子当场逮住，并按在纸上</t>
+  </si>
+  <si>
+    <t>普通东西翻上几页，也能发现自己其实很有优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忠实记录每句话，包括那句“这段千万别写”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纸上的人物开始互相制造麻烦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装得下目标、流程和预算</t>
+  </si>
+  <si>
+    <t>临时委托单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作通行券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别邀请函</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目投标书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传奇推荐信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一张突然送上门的工作，撕下票根就没有犹豫时间</t>
+  </si>
+  <si>
+    <t>有效期和机会一样短暂，验票之后立即失效</t>
+  </si>
+  <si>
+    <t>看起来不像群发的，至少封蜡盖得非常认真</t>
+  </si>
+  <si>
+    <t>把准备与野心装订成册，提交后静候命运翻页</t>
+  </si>
+  <si>
+    <t>有人替你敲开命运的大门，可惜这封信只能用一次</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_3]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_4]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_5]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -255,7 +631,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +653,21 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -588,21 +979,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="74.5546875" customWidth="1"/>
-    <col min="5" max="5" width="64.109375" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="74.5546875" customWidth="1"/>
+    <col min="6" max="6" width="64.109375" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -612,24 +1004,27 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -639,24 +1034,27 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
+      <c r="D2" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>23</v>
+      <c r="F2" t="s">
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -666,24 +1064,27 @@
       <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
+      <c r="D3" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>24</v>
+      <c r="F3" t="s">
+        <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -693,228 +1094,777 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5">
+        <v>33</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>2500</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="D6" s="1">
+        <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6">
+        <v>34</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>4000</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I6" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7">
+      <c r="G7">
         <v>1</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>4000</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I7" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8">
+      <c r="G8">
         <v>1</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>4500</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I8" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
+      </c>
+      <c r="D9" s="1">
+        <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
-      <c r="G9">
-        <v>4000</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <v>3800</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10">
+        <v>28</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>2000</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11">
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11">
         <v>3200</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>3000</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12">
+      <c r="F12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>4200</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>4000</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>19</v>
+        <v>53</v>
+      </c>
+      <c r="D13" s="1">
+        <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>4001</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>21</v>
+        <v>54</v>
+      </c>
+      <c r="D14" s="1">
+        <v>2</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14">
-        <v>3600</v>
+        <v>60</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>4002</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>4003</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>4004</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>4005</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>4006</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>4007</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H20">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>4008</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>4009</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>4010</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="1">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H23">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>4011</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H24">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>4012</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>4013</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>4014</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H27">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>4015</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H28">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>4016</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" t="s">
+        <v>126</v>
+      </c>
+      <c r="H29">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>4017</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30">
+        <v>4</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>4018</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>4019</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>4020</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H33">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>4021</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>4022</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>4023</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36">
+        <v>3</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>4024</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H37">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>4025</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H38">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>4026</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39">
+        <v>4</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H39">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>4027</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0225CF-38BB-4C55-87A1-E98D49777290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A630FF1A-3037-4397-85A5-EDB073FF54F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1160,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>51</v>
@@ -1212,7 +1212,7 @@
         <v>1</v>
       </c>
       <c r="H8">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>48</v>
@@ -1238,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>49</v>
@@ -1860,6 +1860,9 @@
       </c>
       <c r="F40" s="1" t="s">
         <v>140</v>
+      </c>
+      <c r="H40">
+        <v>5500</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A630FF1A-3037-4397-85A5-EDB073FF54F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3858AF-FE90-4727-A930-A51983927DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="24" windowWidth="30696" windowHeight="16536" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="144">
   <si>
     <t>##var</t>
   </si>
@@ -624,6 +624,18 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转盘币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滴滴滴，转盘币！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_wheel_coin]</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -980,21 +992,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="74.5546875" customWidth="1"/>
-    <col min="6" max="6" width="64.109375" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="74.5" customWidth="1"/>
+    <col min="6" max="6" width="64.125" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.88671875" customWidth="1"/>
+    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1024,7 +1036,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1054,7 +1066,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1084,7 +1096,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1114,7 +1126,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1140,7 +1152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1166,7 +1178,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1192,7 +1204,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1218,7 +1230,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1244,7 +1256,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1264,604 +1276,624 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11">
+        <v>1011</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="1">
+        <v>4</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H11">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12">
         <v>2000</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H11">
+      <c r="H12">
         <v>3200</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B13">
         <v>3000</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>4</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="H12">
+      <c r="H13">
         <v>4200</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B13">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B14">
         <v>4000</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14">
-        <v>4001</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H14">
         <v>4000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H15">
         <v>4000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="D16" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>117</v>
+        <v>59</v>
       </c>
       <c r="H16">
         <v>4000</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H17">
         <v>4000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
+        <v>4004</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B19">
         <v>4005</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19">
-        <v>4006</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>4006</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F20" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="H19">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20">
-        <v>4007</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D20" s="1">
-        <v>4</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="H20">
         <v>4500</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21">
+        <v>4007</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" s="1">
+        <v>4</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H21">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22">
         <v>4008</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <v>4009</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" t="s">
-        <v>121</v>
+        <v>81</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="H22">
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D23" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>123</v>
+        <v>82</v>
+      </c>
+      <c r="F23" t="s">
+        <v>121</v>
       </c>
       <c r="H23">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H24">
         <v>4000</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
+        <v>72</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H25">
         <v>4000</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H26">
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H27">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <v>4014</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H27">
+      <c r="H28">
         <v>4200</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B29">
         <v>4015</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H28">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <v>4016</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>4016</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>126</v>
-      </c>
-      <c r="H29">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30">
-        <v>4017</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>130</v>
       </c>
       <c r="H30">
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
+        <v>4017</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H31">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B32">
         <v>4018</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H31">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32">
-        <v>4019</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H32">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33">
+        <v>4019</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H33">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34">
         <v>4020</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H33">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34">
-        <v>4021</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H34">
         <v>4500</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H35">
         <v>4500</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36">
+        <v>4022</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H36">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37">
         <v>4023</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="D36">
-        <v>3</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37">
-        <v>4024</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H37">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <v>4024</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38">
+        <v>3</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F38" t="s">
         <v>136</v>
       </c>
-      <c r="H37">
+      <c r="H38">
         <v>5500</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39">
         <v>4025</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="D38">
-        <v>4</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H38">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39">
-        <v>4026</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H39">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>4026</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F40" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H39">
+      <c r="H40">
         <v>5200</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41">
         <v>4027</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="D40">
+      <c r="D41">
         <v>5</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F41" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H40">
+      <c r="H41">
         <v>5500</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3858AF-FE90-4727-A930-A51983927DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04776AFA-D39A-403B-B4FD-C0DCC6FC84B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="145">
   <si>
     <t>##var</t>
   </si>
@@ -148,18 +148,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>家具折扣券~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘礼盒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘礼盒~</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rewardScale</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -196,446 +184,458 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>凝结着一小段时光的特殊货币，投入时光礼物箱，或许能换回一份来自未来的惊喜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鼓鼓钱袋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一叠模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一枚亮晶晶的模拟币，使用后获取少量模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一叠金灿灿的模拟币，使用后获取一些模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钱袋已经被撑得圆滚滚的，使用后获取中量模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一箱模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>箱子里全是模拟币，使用后获取大量模拟币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>璀璨金库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>现在，需要担心的是该怎么把钱花完</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>useEffect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用奖池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,1000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,5000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,10000,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,100,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,500,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电动踏板车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>厢式货车</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拧下车把，城市的每条小路都能变成赚钱捷径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建筑许可证书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_3]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装得下半座仓库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>薄薄一张纸，却能打开大型工程的厚重大门</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品质</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版式启蒙册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>宣传样机册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>品牌识别手册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>展陈设计证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>灵感数位板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hadeep教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MySOL教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Unlty教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wwb三剑客教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeiX教程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教文字和图片各就各位，拯救摇摇欲坠的海报</t>
+  </si>
+  <si>
+    <t>接住稍纵即逝的灵感，再把它们画成可以交稿的样子</t>
+  </si>
+  <si>
+    <t>提前看看成品，避免创意只活在想象之中</t>
+  </si>
+  <si>
+    <t>让颜色、图形和字体一眼看出是同一家人</t>
+  </si>
+  <si>
+    <t>获得让平面创意站起来，并占满整个展厅的资格</t>
+  </si>
+  <si>
+    <t>集齐结构、样式与交互，网页终于不再各长各的</t>
+  </si>
+  <si>
+    <t>小小页面装下大大功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教一群机器分头搬数据</t>
+  </si>
+  <si>
+    <t>从拖动一个方块开始，不知不觉搭出一整个世界</t>
+  </si>
+  <si>
+    <t>让四处乱跑的数据排好队</t>
+  </si>
+  <si>
+    <t>灵感钢笔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖点卡册</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采访录音笔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧本打字机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>策划档案箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础维修工具包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管路维护套装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能万用表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型检修箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>精密校准箱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东西不算多，但足够让坏掉的家电重新反省</t>
+  </si>
+  <si>
+    <t>专治滴答作响，以及半夜突然有想法的水管</t>
+  </si>
+  <si>
+    <t>电路虽然不会说话，但屏幕上的波形很会告密</t>
+  </si>
+  <si>
+    <t>拧紧螺丝已经不够，让整台设备重新升级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专门处理肉眼看不见、维修报价却看得很清楚的问题</t>
+  </si>
+  <si>
+    <t>负责把路过脑海的句子当场逮住，并按在纸上</t>
+  </si>
+  <si>
+    <t>普通东西翻上几页，也能发现自己其实很有优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>忠实记录每句话，包括那句“这段千万别写”</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纸上的人物开始互相制造麻烦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>装得下目标、流程和预算</t>
+  </si>
+  <si>
+    <t>临时委托单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作通行券</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>特别邀请函</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目投标书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传奇推荐信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一张突然送上门的工作，撕下票根就没有犹豫时间</t>
+  </si>
+  <si>
+    <t>有效期和机会一样短暂，验票之后立即失效</t>
+  </si>
+  <si>
+    <t>看起来不像群发的，至少封蜡盖得非常认真</t>
+  </si>
+  <si>
+    <t>把准备与野心装订成册，提交后静候命运翻页</t>
+  </si>
+  <si>
+    <t>有人替你敲开命运的大门，可惜这封信只能用一次</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_3]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_4]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_2]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_2]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_1]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_3]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_4]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_5]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>转盘币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滴滴滴，转盘币！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_wheel_coin]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初级零工凭证礼盒</t>
+  </si>
+  <si>
+    <t>里面包含各类初级零工所需的凭证，有较小概率获得中级零工凭证</t>
+  </si>
+  <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_gift_box]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>凝结着一小段时光的特殊货币，投入时光礼物箱，或许能换回一份来自未来的惊喜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鼓鼓钱袋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一叠模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一枚亮晶晶的模拟币，使用后获取少量模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一叠金灿灿的模拟币，使用后获取一些模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>钱袋已经被撑得圆滚滚的，使用后获取中量模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一箱模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>箱子里全是模拟币，使用后获取大量模拟币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>璀璨金库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>现在，需要担心的是该怎么把钱花完</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_coin_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>useEffect</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c,s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用奖池</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,1000,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,5000,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,10000,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,100,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,500,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_coin]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电动踏板车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>厢式货车</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拧下车把，城市的每条小路都能变成赚钱捷径</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建筑许可证书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_3]</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_base_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>装得下半座仓库</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>薄薄一张纸，却能打开大型工程的厚重大门</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c,s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品质</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>版式启蒙册</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>宣传样机册</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>品牌识别手册</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>展陈设计证</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>灵感数位板</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hadeep教程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MySOL教程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Unlty教程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wwb三剑客教程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WeiX教程</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教文字和图片各就各位，拯救摇摇欲坠的海报</t>
-  </si>
-  <si>
-    <t>接住稍纵即逝的灵感，再把它们画成可以交稿的样子</t>
-  </si>
-  <si>
-    <t>提前看看成品，避免创意只活在想象之中</t>
-  </si>
-  <si>
-    <t>让颜色、图形和字体一眼看出是同一家人</t>
-  </si>
-  <si>
-    <t>获得让平面创意站起来，并占满整个展厅的资格</t>
-  </si>
-  <si>
-    <t>集齐结构、样式与交互，网页终于不再各长各的</t>
-  </si>
-  <si>
-    <t>小小页面装下大大功能</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教一群机器分头搬数据</t>
-  </si>
-  <si>
-    <t>从拖动一个方块开始，不知不觉搭出一整个世界</t>
-  </si>
-  <si>
-    <t>让四处乱跑的数据排好队</t>
-  </si>
-  <si>
-    <t>灵感钢笔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卖点卡册</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>采访录音笔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>剧本打字机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>策划档案箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础维修工具包</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>管路维护套装</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>智能万用表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>重型检修箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>精密校准箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>东西不算多，但足够让坏掉的家电重新反省</t>
-  </si>
-  <si>
-    <t>专治滴答作响，以及半夜突然有想法的水管</t>
-  </si>
-  <si>
-    <t>电路虽然不会说话，但屏幕上的波形很会告密</t>
-  </si>
-  <si>
-    <t>拧紧螺丝已经不够，让整台设备重新升级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>专门处理肉眼看不见、维修报价却看得很清楚的问题</t>
-  </si>
-  <si>
-    <t>负责把路过脑海的句子当场逮住，并按在纸上</t>
-  </si>
-  <si>
-    <t>普通东西翻上几页，也能发现自己其实很有优势</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>忠实记录每句话，包括那句“这段千万别写”</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纸上的人物开始互相制造麻烦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>装得下目标、流程和预算</t>
-  </si>
-  <si>
-    <t>临时委托单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作通行券</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>特别邀请函</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目投标书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>传奇推荐信</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一张突然送上门的工作，撕下票根就没有犹豫时间</t>
-  </si>
-  <si>
-    <t>有效期和机会一样短暂，验票之后立即失效</t>
-  </si>
-  <si>
-    <t>看起来不像群发的，至少封蜡盖得非常认真</t>
-  </si>
-  <si>
-    <t>把准备与野心装订成册，提交后静候命运翻页</t>
-  </si>
-  <si>
-    <t>有人替你敲开命运的大门，可惜这封信只能用一次</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_3]</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_art_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_2]</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_it_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_4]</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_fix_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_2]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_write_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_2]</t>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_1]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_3]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_4]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_work_luck_5]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>转盘币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>滴滴滴，转盘币！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_wheel_coin]</t>
+  </si>
+  <si>
+    <t>4000,1,50;4001,1,50;4002,1,1;4003,1,50;4004,1,50;4005,1,1;4006,1,1;4008,1,50;4009,1,50;4010,1,1;4011,1,1;4013,1,50;4014,1,50;4015,1,1;4016,1,1;4018,1,50;4019,1,50;4020,1,1;4021,1,1;4023,1,10;4024,1,1</t>
+  </si>
+  <si>
+    <t>搬空家具城指日可待！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -993,20 +993,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="74.5" customWidth="1"/>
-    <col min="6" max="6" width="64.125" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="74.44140625" customWidth="1"/>
+    <col min="6" max="6" width="64.109375" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
@@ -1026,17 +1026,17 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1047,7 +1047,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -1056,17 +1056,17 @@
         <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1086,17 +1086,17 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1107,7 +1107,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>12</v>
@@ -1116,31 +1116,31 @@
         <v>13</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1149,24 +1149,24 @@
         <v>2500</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1175,24 +1175,24 @@
         <v>3000</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G7">
         <v>1</v>
@@ -1201,24 +1201,24 @@
         <v>4000</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1">
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1227,24 +1227,24 @@
         <v>4000</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>5</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1253,50 +1253,50 @@
         <v>3200</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H10">
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1011</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H11">
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>2000</v>
       </c>
@@ -1305,30 +1305,30 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>15</v>
+        <v>144</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H12">
         <v>3200</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>3000</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="D13" s="1">
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1336,562 +1336,565 @@
       <c r="H13">
         <v>4200</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="I13" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>4000</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D14" s="1">
         <v>2</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H14">
         <v>4000</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>4001</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1">
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H15">
         <v>4000</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>4002</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1">
         <v>3</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="H16">
         <v>4000</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>4003</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H17">
         <v>4000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>4004</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H18">
         <v>4000</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>4005</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H19">
         <v>3800</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>4006</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D20" s="1">
         <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H20">
         <v>4500</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>4007</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D21" s="1">
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H21">
         <v>4500</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>4008</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H22">
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>4009</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D23" s="1">
         <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H23">
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>4010</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H24">
         <v>4000</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>4011</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D25" s="1">
         <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H25">
         <v>4000</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>4012</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H26">
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>4013</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D27">
         <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H27">
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>4014</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D28">
         <v>2</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H28">
         <v>4200</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>4015</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D29">
         <v>3</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H29">
         <v>4400</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>4016</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H30">
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>4017</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D31">
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H31">
         <v>4000</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>4018</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H32">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>4019</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D33">
         <v>2</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H33">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>4020</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H34">
         <v>4500</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>4021</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D35">
         <v>3</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H35">
         <v>4500</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>4022</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D36">
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H36">
         <v>4500</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>4023</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H37">
         <v>5000</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>4024</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F38" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H38">
         <v>5500</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>4025</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="H39">
         <v>5000</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>4026</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D40">
         <v>4</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H40">
         <v>5200</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>4027</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D41">
         <v>5</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H41">
         <v>5500</v>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04776AFA-D39A-403B-B4FD-C0DCC6FC84B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EDF1C0-FE97-4C6A-949F-76D337D868AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="161">
   <si>
     <t>##var</t>
   </si>
@@ -637,6 +637,63 @@
   <si>
     <t>搬空家具城指日可待！</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创可贴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>稍微治疗一下你的伤势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元气胶囊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃下这颗胶囊就好啦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>医疗包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>里面什么都有，帮助你快速恢复健康</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[medical_item_bandage]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[medical_item_vitality_capsule]</t>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[medical_item_kit]</t>
+  </si>
+  <si>
+    <t>102,5,100</t>
+  </si>
+  <si>
+    <t>102,5,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>202,5,200</t>
+  </si>
+  <si>
+    <t>302,5,300</t>
+  </si>
+  <si>
+    <t>102,10,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102,15,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02,5,00</t>
   </si>
 </sst>
 </file>
@@ -992,21 +1049,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="74.44140625" customWidth="1"/>
-    <col min="6" max="6" width="64.109375" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="5" max="5" width="74.5" customWidth="1"/>
+    <col min="6" max="6" width="64.125" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.88671875" customWidth="1"/>
+    <col min="8" max="8" width="21.5" customWidth="1"/>
+    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1093,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1066,7 +1123,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1096,7 +1153,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1126,7 +1183,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1152,7 +1209,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1178,7 +1235,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1204,7 +1261,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1230,7 +1287,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1256,7 +1313,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1276,7 +1333,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1296,607 +1353,687 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B12">
-        <v>2000</v>
+        <v>1050</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1"/>
+        <v>145</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>151</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B13">
-        <v>3000</v>
+        <v>1051</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="D13" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>4200</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4000</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14">
-        <v>4000</v>
+        <v>1052</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
       <c r="D14" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>51</v>
+        <v>150</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>53</v>
+        <v>153</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
       </c>
       <c r="H14">
         <v>4000</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I14" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15">
-        <v>4001</v>
+        <v>2000</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="H15">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>3000</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="1">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>4200</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B17">
         <v>4000</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>4002</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="1">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H16">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17">
-        <v>4003</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D17" s="1">
         <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="H17">
         <v>4000</v>
       </c>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18">
-        <v>4004</v>
+        <v>4001</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="H18">
         <v>4000</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19">
-        <v>4005</v>
+        <v>4002</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D19" s="1">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>4003</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H20">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <v>4004</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H21">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <v>4005</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D22" s="1">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F22" t="s">
         <v>112</v>
       </c>
-      <c r="H19">
+      <c r="H22">
         <v>3800</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B20">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B23">
         <v>4006</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D23" s="1">
         <v>3</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E23" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F23" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H20">
+      <c r="H23">
         <v>4500</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B24">
         <v>4007</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D24" s="1">
         <v>4</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E24" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H21">
+      <c r="H24">
         <v>4500</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B25">
         <v>4008</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D25" s="1">
         <v>2</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E25" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="H22">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <v>4009</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F23" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <v>4010</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H24">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25">
-        <v>4011</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="1">
-        <v>3</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="H25">
         <v>4000</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26">
-        <v>4012</v>
+        <v>4009</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26">
-        <v>4</v>
+        <v>71</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>121</v>
+        <v>78</v>
+      </c>
+      <c r="F26" t="s">
+        <v>117</v>
       </c>
       <c r="H26">
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27">
-        <v>4013</v>
+        <v>4010</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27">
-        <v>2</v>
+        <v>67</v>
+      </c>
+      <c r="D27" s="1">
+        <v>3</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H27">
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28">
-        <v>4014</v>
+        <v>4011</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28">
+        <v>68</v>
+      </c>
+      <c r="D28" s="1">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H28">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <v>4012</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <v>4013</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30">
         <v>2</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="H28">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <v>4015</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H29">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30">
-        <v>4016</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" t="s">
-        <v>122</v>
+        <v>92</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="H30">
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31">
+        <v>4014</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H31">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <v>4015</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <v>4016</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" t="s">
+        <v>122</v>
+      </c>
+      <c r="H33">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34">
         <v>4017</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D31">
+      <c r="D34">
         <v>4</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F34" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H31">
+      <c r="H34">
         <v>4000</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35">
         <v>4018</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D32">
+      <c r="D35">
         <v>2</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E35" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H32">
+      <c r="H35">
         <v>5500</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36">
         <v>4019</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D33">
+      <c r="D36">
         <v>2</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H33">
+      <c r="H36">
         <v>5500</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37">
         <v>4020</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D34">
-        <v>3</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H34">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35">
-        <v>4021</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H35">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36">
-        <v>4022</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D36">
-        <v>4</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H36">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37">
-        <v>4023</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="D37">
         <v>3</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H37">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38">
-        <v>4024</v>
+        <v>4021</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F38" t="s">
-        <v>132</v>
+        <v>100</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="H38">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39">
-        <v>4025</v>
+        <v>4022</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D39">
         <v>4</v>
       </c>
       <c r="E39" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H39">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40">
+        <v>4023</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H40">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41">
+        <v>4024</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F41" t="s">
+        <v>132</v>
+      </c>
+      <c r="H41">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <v>4025</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D42">
+        <v>4</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H39">
+      <c r="H42">
         <v>5000</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43">
         <v>4026</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D40">
+      <c r="D43">
         <v>4</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H40">
+      <c r="H43">
         <v>5200</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44">
         <v>4027</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D41">
+      <c r="D44">
         <v>5</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H41">
+      <c r="H44">
         <v>5500</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EDF1C0-FE97-4C6A-949F-76D337D868AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D37657-6529-4143-9C64-93E29551F4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="157">
   <si>
     <t>##var</t>
   </si>
@@ -672,28 +672,16 @@
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[medical_item_kit]</t>
   </si>
   <si>
-    <t>102,5,100</t>
-  </si>
-  <si>
-    <t>102,5,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>202,5,200</t>
-  </si>
-  <si>
-    <t>302,5,300</t>
-  </si>
-  <si>
-    <t>102,10,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>102,15,100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>02,5,00</t>
+    <t>103,5,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103,10,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103,15,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1376,7 +1364,7 @@
         <v>4000</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
@@ -1402,7 +1390,7 @@
         <v>4000</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1428,7 +1416,7 @@
         <v>4000</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D37657-6529-4143-9C64-93E29551F4EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805ED9D5-CC60-4515-BBD5-4DFBDA262E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,8 @@
           <t xml:space="preserve">
 2000 为一些功能性道具
 3000 为一些稀有道具
-4000 为零工所需道具</t>
+4000 为零工所需道具
+5000 材料道具</t>
         </r>
       </text>
     </comment>
@@ -100,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="172">
   <si>
     <t>##var</t>
   </si>
@@ -682,6 +683,63 @@
   <si>
     <t>103,15,100</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>秘匣币</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘟嘟嘟，秘匣币！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_lottery_secret_box_coin]</t>
+  </si>
+  <si>
+    <t>野生狗奶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一切秩序即将崩塌，宇宙论为一片死寂虚空，而野生狗奶依旧存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_wild_dog_milk]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>活虾(死亡)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>量子叠加，薛定谔的终极定理，超出三界之外，不在五行之中，售价十四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_live_shrimp(dead)]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免费米饭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_free_rice_two_yuan]</t>
+  </si>
+  <si>
+    <t>最后的考古学家在虚空尽头挖出一块牌子，写着：”免费米饭，两元"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>春秋肠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃下它，你将重新站在那个岔路口，再一次，做出同样的选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_spring_autumn_ham]</t>
   </si>
 </sst>
 </file>
@@ -1037,21 +1095,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="13.5" customWidth="1"/>
-    <col min="5" max="5" width="74.5" customWidth="1"/>
-    <col min="6" max="6" width="64.125" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="74.44140625" customWidth="1"/>
+    <col min="6" max="6" width="64.109375" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21.5" customWidth="1"/>
-    <col min="9" max="9" width="21.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.875" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1139,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1111,7 +1169,7 @@
       </c>
       <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1141,7 +1199,7 @@
       </c>
       <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1171,7 +1229,7 @@
       </c>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1197,7 +1255,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1223,7 +1281,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1249,7 +1307,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1275,7 +1333,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1301,7 +1359,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1321,7 +1379,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1341,47 +1399,41 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12">
+        <v>1012</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H12">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13">
         <v>1050</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>4000</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B13">
-        <v>1051</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="1">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1390,24 +1442,24 @@
         <v>4000</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D14" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1416,613 +1468,719 @@
         <v>4000</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>1052</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D15" s="1">
+        <v>3</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>4000</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B15">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16">
         <v>2000</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H15">
+      <c r="H16">
         <v>3200</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B16">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>3000</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C17" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D17" s="1">
         <v>4</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G16">
+      <c r="G17">
         <v>1</v>
       </c>
-      <c r="H16">
+      <c r="H17">
         <v>4200</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18">
         <v>4000</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C18" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H17">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B18">
-        <v>4001</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D18" s="1">
         <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H18">
         <v>4000</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19">
-        <v>4002</v>
+        <v>4001</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H19">
         <v>4000</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20">
-        <v>4003</v>
+        <v>4002</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D20" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="H20">
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21">
-        <v>4004</v>
+        <v>4003</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H21">
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22">
+        <v>4004</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="H22">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23">
         <v>4005</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D22" s="1">
-        <v>3</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B23">
-        <v>4006</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="D23" s="1">
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>4006</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="1">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F24" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="H23">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B24">
-        <v>4007</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="1">
-        <v>4</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="H24">
         <v>4500</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25">
+        <v>4007</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="1">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>4008</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B26">
-        <v>4009</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D26" s="1">
         <v>2</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F26" t="s">
-        <v>117</v>
+        <v>77</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="H26">
         <v>4000</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27">
-        <v>4010</v>
+        <v>4009</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D27" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
+      </c>
+      <c r="F27" t="s">
+        <v>117</v>
       </c>
       <c r="H27">
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28">
-        <v>4011</v>
+        <v>4010</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D28" s="1">
         <v>3</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H28">
         <v>4000</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29">
-        <v>4012</v>
+        <v>4011</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
+        <v>68</v>
+      </c>
+      <c r="D29" s="1">
+        <v>3</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H29">
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30">
-        <v>4013</v>
+        <v>4012</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H30">
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>4014</v>
+        <v>4013</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H31">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>4014</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F32" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H31">
+      <c r="H32">
         <v>4200</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B32">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33">
         <v>4015</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H32">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B33">
-        <v>4016</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D33">
         <v>3</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H33">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>4016</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34">
+        <v>3</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>122</v>
-      </c>
-      <c r="H33">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B34">
-        <v>4017</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>126</v>
       </c>
       <c r="H34">
         <v>4000</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35">
+        <v>4017</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H35">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36">
         <v>4018</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H35">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B36">
-        <v>4019</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="D36">
         <v>2</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H36">
         <v>5500</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37">
+        <v>4019</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37">
+        <v>2</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38">
         <v>4020</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D37">
-        <v>3</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H37">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B38">
-        <v>4021</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="D38">
         <v>3</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H38">
         <v>4500</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H39">
         <v>4500</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40">
+        <v>4022</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D40">
+        <v>4</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H40">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B41">
         <v>4023</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="D40">
-        <v>3</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H40">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B41">
-        <v>4024</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="D41">
         <v>3</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H41">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>4024</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>132</v>
       </c>
-      <c r="H41">
+      <c r="H42">
         <v>5500</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B42">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B43">
         <v>4025</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="H42">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B43">
-        <v>4026</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="D43">
         <v>4</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H43">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B44">
+        <v>4026</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F44" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H43">
+      <c r="H44">
         <v>5200</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B44">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B45">
         <v>4027</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D44">
+      <c r="D45">
         <v>5</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F45" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H44">
+      <c r="H45">
         <v>5500</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>5000</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H46">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>5001</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H47">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>5002</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F48" t="s">
+        <v>167</v>
+      </c>
+      <c r="H48">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>5003</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F49" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49">
+        <v>7000</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805ED9D5-CC60-4515-BBD5-4DFBDA262E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5F21A8-AF7B-451E-ABB0-E045492DC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="177">
   <si>
     <t>##var</t>
   </si>
@@ -740,6 +740,25 @@
   </si>
   <si>
     <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_spring_autumn_ham]</t>
+  </si>
+  <si>
+    <t>社区物资礼盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社区给居民提交材料的回馈奖励，可以获得各种物资</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,100,100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>道具类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1095,21 +1114,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" customWidth="1"/>
-    <col min="5" max="5" width="74.44140625" customWidth="1"/>
-    <col min="6" max="6" width="64.109375" customWidth="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" customWidth="1"/>
-    <col min="9" max="9" width="21.44140625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="26.88671875" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="79.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="181.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1123,23 +1144,26 @@
         <v>58</v>
       </c>
       <c r="E1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1153,23 +1177,26 @@
         <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
+      <c r="G2" t="s">
+        <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1188,18 +1215,21 @@
       <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
+      <c r="G3" t="s">
+        <v>9</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1212,24 +1242,27 @@
       <c r="D4" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1239,23 +1272,26 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
       <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
         <v>2500</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1265,23 +1301,26 @@
       <c r="D6" s="1">
         <v>2</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
       <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>3000</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1291,23 +1330,26 @@
       <c r="D7" s="1">
         <v>3</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
       <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
         <v>4000</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1317,23 +1359,26 @@
       <c r="D8" s="1">
         <v>4</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
       <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
         <v>4000</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1343,23 +1388,26 @@
       <c r="D9" s="1">
         <v>5</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
         <v>3200</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1369,17 +1417,20 @@
       <c r="D10" s="1">
         <v>3</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1389,17 +1440,20 @@
       <c r="D11" s="1">
         <v>4</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1012</v>
       </c>
@@ -1409,17 +1463,20 @@
       <c r="D12" s="1">
         <v>4</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>3500</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1050</v>
       </c>
@@ -1429,23 +1486,26 @@
       <c r="D13" s="1">
         <v>1</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
       <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
         <v>4000</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1051</v>
       </c>
@@ -1455,23 +1515,26 @@
       <c r="D14" s="1">
         <v>2</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
       <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
         <v>4000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1052</v>
       </c>
@@ -1481,23 +1544,26 @@
       <c r="D15" s="1">
         <v>3</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
       <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
         <v>4000</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>2000</v>
       </c>
@@ -1507,17 +1573,20 @@
       <c r="D16" s="1">
         <v>1</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>3200</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>3000</v>
       </c>
@@ -1527,659 +1596,787 @@
       <c r="D17" s="1">
         <v>4</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
       <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
         <v>4200</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18">
+        <v>3001</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" s="1">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>4200</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>4000</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C19" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19">
-        <v>4001</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D19" s="1">
         <v>2</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19">
+        <v>4</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I19">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>4001</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H19">
+      <c r="I20">
         <v>4000</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B20">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>4002</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>3</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E21">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H20">
+      <c r="I21">
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B21">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22">
         <v>4003</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C22" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H21">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22">
-        <v>4004</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="D22" s="1">
         <v>2</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>4004</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23">
+        <v>4</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H22">
+      <c r="I23">
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>4005</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C24" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F23" t="s">
-        <v>112</v>
-      </c>
-      <c r="H23">
-        <v>3800</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24">
-        <v>4006</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="D24" s="1">
         <v>3</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G24" t="s">
+        <v>112</v>
+      </c>
+      <c r="I24">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>4006</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="1">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>4</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H24">
+      <c r="I25">
         <v>4500</v>
       </c>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>4007</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="1">
-        <v>4</v>
-      </c>
-      <c r="E25" s="1" t="s">
+      <c r="D26" s="1">
+        <v>4</v>
+      </c>
+      <c r="E26">
+        <v>4</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H25">
+      <c r="I26">
         <v>4500</v>
       </c>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B26">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27">
         <v>4008</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H26">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B27">
-        <v>4009</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="D27" s="1">
         <v>2</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I27">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>4009</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G28" t="s">
         <v>117</v>
       </c>
-      <c r="H27">
+      <c r="I28">
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B28">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29">
         <v>4010</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H28">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29">
-        <v>4011</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="D29" s="1">
         <v>3</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I29">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>4011</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="1">
+        <v>3</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H29">
+      <c r="I30">
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31">
         <v>4012</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D30">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="G31" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H30">
+      <c r="I31">
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32">
         <v>4013</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="D31">
-        <v>2</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H31">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32">
-        <v>4014</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="D32">
         <v>2</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I32">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>4014</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="G33" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H32">
+      <c r="I33">
         <v>4200</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34">
         <v>4015</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H33">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34">
-        <v>4016</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="D34">
         <v>3</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I34">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>4016</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G35" t="s">
         <v>122</v>
       </c>
-      <c r="H34">
+      <c r="I35">
         <v>4000</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36">
         <v>4017</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D35">
-        <v>4</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>4</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="G36" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="H35">
+      <c r="I36">
         <v>4000</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37">
         <v>4018</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C37" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H36">
-        <v>5500</v>
-      </c>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37">
-        <v>4019</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="D37">
         <v>2</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37">
+        <v>4</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I37">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>4019</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H37">
+      <c r="I38">
         <v>5500</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39">
         <v>4020</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="D38">
-        <v>3</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H38">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39">
-        <v>4021</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39">
+        <v>4</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I39">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>4021</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>4</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H39">
+      <c r="I40">
         <v>4500</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41">
         <v>4022</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D40">
-        <v>4</v>
-      </c>
-      <c r="E40" s="1" t="s">
+      <c r="D41">
+        <v>4</v>
+      </c>
+      <c r="E41">
+        <v>4</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H40">
+      <c r="I41">
         <v>4500</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B41">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42">
         <v>4023</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C42" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="D41">
-        <v>3</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H41">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B42">
-        <v>4024</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="D42">
         <v>3</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42">
+        <v>4</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I42">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>4024</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>4</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G43" t="s">
         <v>132</v>
       </c>
-      <c r="H42">
+      <c r="I43">
         <v>5500</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B43">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44">
         <v>4025</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D43">
-        <v>4</v>
-      </c>
-      <c r="E43" s="1" t="s">
+      <c r="D44">
+        <v>4</v>
+      </c>
+      <c r="E44">
+        <v>4</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H43">
+      <c r="I44">
         <v>5000</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B44">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45">
         <v>4026</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D44">
-        <v>4</v>
-      </c>
-      <c r="E44" s="1" t="s">
+      <c r="D45">
+        <v>4</v>
+      </c>
+      <c r="E45">
+        <v>4</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="G45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H44">
+      <c r="I45">
         <v>5200</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B45">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46">
         <v>4027</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D45">
+      <c r="D46">
         <v>5</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="H45">
+      <c r="I46">
         <v>5500</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47">
         <v>5000</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C47" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="D46">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H46">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47">
-        <v>5001</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="D47">
         <v>3</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>164</v>
+      <c r="E47">
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="H47">
+        <v>161</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I47">
         <v>6000</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48">
-        <v>5002</v>
+        <v>5001</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D48">
         <v>3</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F48" t="s">
-        <v>167</v>
-      </c>
-      <c r="H48">
+      <c r="E48">
+        <v>5</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="I48">
         <v>6000</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B49">
-        <v>5003</v>
+        <v>5002</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D49">
         <v>3</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49">
+        <v>5</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G49" t="s">
+        <v>167</v>
+      </c>
+      <c r="I49">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>5003</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G50" t="s">
         <v>171</v>
       </c>
-      <c r="H49">
+      <c r="I50">
         <v>7000</v>
       </c>
     </row>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5F21A8-AF7B-451E-ABB0-E045492DC11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9AC7FB-FD51-43B9-AEDC-E23CE76FAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,7 +101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="180">
   <si>
     <t>##var</t>
   </si>
@@ -758,6 +758,17 @@
   </si>
   <si>
     <t>道具类别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小鸡手办</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[icon_basketball_trainee_chicken]</t>
+  </si>
+  <si>
+    <t>似曾相识故人来</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1114,7 +1125,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
@@ -2380,6 +2391,29 @@
         <v>7000</v>
       </c>
     </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>5004</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>5</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I51">
+        <v>6000</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MiniTemplate/Datas/item.xlsx
+++ b/MiniTemplate/Datas/item.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9AC7FB-FD51-43B9-AEDC-E23CE76FAB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F3BB58-36F5-4AA9-A21F-C08E53B4010C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,8 @@
 2000 为一些功能性道具
 3000 为一些稀有道具
 4000 为零工所需道具
-5000 材料道具</t>
+5000 材料道具
+6000 鱼</t>
         </r>
       </text>
     </comment>
@@ -101,7 +102,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="207">
   <si>
     <t>##var</t>
   </si>
@@ -769,6 +770,114 @@
   </si>
   <si>
     <t>似曾相识故人来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小白条</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_01_white_strip]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河鲫鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总爱成群贴着水面穿梭，个头不大，逃跑时倒是格外认真</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河畔最常见的老住户，性情温和，似乎已经看惯了岸边的钓鱼人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_02_crucian]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小泥鳅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>身体滑溜得几乎抓不住，一眨眼就能钻进河底的泥沙里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Assets/Art/Common/SpriteAtlasIcon.spriteatlasv2[fish_03_loach]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>红尾鲤鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青草鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银鲢鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河鲈鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>花鳜鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蓝须鲶鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>福运锦鲤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月辉鳟鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时光游鱼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摆动鲜艳的红色尾鳍缓缓游过，据说遇见它会带来一点小好运</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜欢藏在水草丰茂的地方，胃口很好，几乎从不浪费任何一片嫩叶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>银亮的鱼身会映出水面的天光，受到惊吓时常会突然跃出水面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>披着整齐的深色条纹，是河中敏捷的猎手，上钩后依然很有力气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>华丽斑纹是天然的伪装，静止时几乎能与河底的碎石融为一体</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长长的胡须可以感知水流变化，即使在昏暗的河底也不会迷路</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>白橙相间的鳞片十分耀眼，传说放进水缸里，家中的好运会悄悄增加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>只在月光洒满河面时出现，游过之后，水中会留下一道淡淡的银蓝微光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳞片间流动着细小的时间刻度，据说凝视它太久，会想起一段已经遗忘的往事</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1125,23 +1234,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K63"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="79.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="181.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.88671875" customWidth="1"/>
+    <col min="1" max="1" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="79.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="181.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1174,7 +1283,7 @@
       </c>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1207,7 +1316,7 @@
       </c>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1240,7 +1349,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1273,7 +1382,7 @@
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1000</v>
       </c>
@@ -1302,7 +1411,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>1001</v>
       </c>
@@ -1331,7 +1440,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1002</v>
       </c>
@@ -1360,7 +1469,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>1003</v>
       </c>
@@ -1389,7 +1498,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>1004</v>
       </c>
@@ -1418,7 +1527,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>1010</v>
       </c>
@@ -1441,7 +1550,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>1011</v>
       </c>
@@ -1464,7 +1573,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>1012</v>
       </c>
@@ -1487,7 +1596,7 @@
         <v>3500</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>1050</v>
       </c>
@@ -1516,7 +1625,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>1051</v>
       </c>
@@ -1545,7 +1654,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>1052</v>
       </c>
@@ -1574,7 +1683,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>2000</v>
       </c>
@@ -1597,7 +1706,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>3000</v>
       </c>
@@ -1626,7 +1735,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>3001</v>
       </c>
@@ -1655,7 +1764,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>4000</v>
       </c>
@@ -1678,7 +1787,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>4001</v>
       </c>
@@ -1701,7 +1810,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>4002</v>
       </c>
@@ -1724,7 +1833,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>4003</v>
       </c>
@@ -1747,7 +1856,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>4004</v>
       </c>
@@ -1770,7 +1879,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>4005</v>
       </c>
@@ -1793,7 +1902,7 @@
         <v>3800</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>4006</v>
       </c>
@@ -1816,7 +1925,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>4007</v>
       </c>
@@ -1839,7 +1948,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>4008</v>
       </c>
@@ -1862,7 +1971,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>4009</v>
       </c>
@@ -1885,7 +1994,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>4010</v>
       </c>
@@ -1908,7 +2017,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>4011</v>
       </c>
@@ -1931,7 +2040,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>4012</v>
       </c>
@@ -1954,7 +2063,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>4013</v>
       </c>
@@ -1977,7 +2086,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33">
         <v>4014</v>
       </c>
@@ -2000,7 +2109,7 @@
         <v>4200</v>
       </c>
     </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B34">
         <v>4015</v>
       </c>
@@ -2023,7 +2132,7 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35">
         <v>4016</v>
       </c>
@@ -2046,7 +2155,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36">
         <v>4017</v>
       </c>
@@ -2069,7 +2178,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37">
         <v>4018</v>
       </c>
@@ -2092,7 +2201,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38">
         <v>4019</v>
       </c>
@@ -2115,7 +2224,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B39">
         <v>4020</v>
       </c>
@@ -2138,7 +2247,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40">
         <v>4021</v>
       </c>
@@ -2161,7 +2270,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41">
         <v>4022</v>
       </c>
@@ -2184,7 +2293,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42">
         <v>4023</v>
       </c>
@@ -2207,7 +2316,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43">
         <v>4024</v>
       </c>
@@ -2230,7 +2339,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>4025</v>
       </c>
@@ -2253,7 +2362,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45">
         <v>4026</v>
       </c>
@@ -2276,7 +2385,7 @@
         <v>5200</v>
       </c>
     </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46">
         <v>4027</v>
       </c>
@@ -2299,7 +2408,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47">
         <v>5000</v>
       </c>
@@ -2322,7 +2431,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48">
         <v>5001</v>
       </c>
@@ -2345,7 +2454,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49">
         <v>5002</v>
       </c>
@@ -2368,7 +2477,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50">
         <v>5003</v>
       </c>
@@ -2391,7 +2500,7 @@
         <v>7000</v>
       </c>
     </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51">
         <v>5004</v>
       </c>
@@ -2412,6 +2521,228 @@
       </c>
       <c r="I51">
         <v>6000</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B52">
+        <v>6000</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>6</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="I52">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B53">
+        <v>6001</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>6</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I53">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B54">
+        <v>6002</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>6</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I54">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B55">
+        <v>6003</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55">
+        <v>6</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B56">
+        <v>6004</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
+      <c r="E56">
+        <v>6</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B57">
+        <v>6005</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+      <c r="E57">
+        <v>6</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B58">
+        <v>6006</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58">
+        <v>6</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B59">
+        <v>6007</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>6</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B60">
+        <v>6008</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D60">
+        <v>3</v>
+      </c>
+      <c r="E60">
+        <v>6</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B61">
+        <v>6009</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+      <c r="E61">
+        <v>6</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B62">
+        <v>6010</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62">
+        <v>4</v>
+      </c>
+      <c r="E62">
+        <v>6</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B63">
+        <v>6011</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63">
+        <v>6</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
